--- a/config/knowledgegraph.xlsx
+++ b/config/knowledgegraph.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\python\NLP\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6897B4D-DA67-439D-BCFA-AEB9719452B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57170985-1870-42F4-A479-802CAE5C7B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11991" uniqueCount="2166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12054" uniqueCount="2167">
   <si>
     <t>一级部位</t>
   </si>
@@ -7490,6 +7490,10 @@
   </si>
   <si>
     <t>下腔静脉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>上腹</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -25961,9 +25965,12 @@
         <v>1124</v>
       </c>
       <c r="B768" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C768" t="s">
         <v>2143</v>
       </c>
-      <c r="C768" t="s">
+      <c r="D768" t="s">
         <v>899</v>
       </c>
       <c r="G768">
@@ -25981,9 +25988,12 @@
         <v>1124</v>
       </c>
       <c r="B769" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C769" t="s">
         <v>2143</v>
       </c>
-      <c r="C769" t="s">
+      <c r="D769" t="s">
         <v>894</v>
       </c>
       <c r="G769">
@@ -26001,9 +26011,12 @@
         <v>1124</v>
       </c>
       <c r="B770" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C770" t="s">
         <v>2143</v>
       </c>
-      <c r="C770" t="s">
+      <c r="D770" t="s">
         <v>1819</v>
       </c>
       <c r="G770">
@@ -26021,9 +26034,12 @@
         <v>1124</v>
       </c>
       <c r="B771" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C771" t="s">
         <v>2143</v>
       </c>
-      <c r="C771" t="s">
+      <c r="D771" t="s">
         <v>1818</v>
       </c>
       <c r="G771">
@@ -26041,9 +26057,12 @@
         <v>1124</v>
       </c>
       <c r="B772" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C772" t="s">
         <v>2143</v>
       </c>
-      <c r="C772" t="s">
+      <c r="D772" t="s">
         <v>1817</v>
       </c>
       <c r="G772">
@@ -26061,9 +26080,12 @@
         <v>1124</v>
       </c>
       <c r="B773" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C773" t="s">
         <v>2143</v>
       </c>
-      <c r="C773" t="s">
+      <c r="D773" t="s">
         <v>897</v>
       </c>
       <c r="G773">
@@ -26081,9 +26103,12 @@
         <v>1124</v>
       </c>
       <c r="B774" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C774" t="s">
         <v>2143</v>
       </c>
-      <c r="C774" t="s">
+      <c r="D774" t="s">
         <v>896</v>
       </c>
       <c r="G774">
@@ -26101,9 +26126,12 @@
         <v>1124</v>
       </c>
       <c r="B775" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C775" t="s">
         <v>2143</v>
       </c>
-      <c r="C775" t="s">
+      <c r="D775" t="s">
         <v>898</v>
       </c>
       <c r="G775">
@@ -26121,9 +26149,12 @@
         <v>1124</v>
       </c>
       <c r="B776" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C776" t="s">
         <v>1125</v>
       </c>
-      <c r="C776" t="s">
+      <c r="D776" t="s">
         <v>2146</v>
       </c>
       <c r="G776">
@@ -26141,9 +26172,12 @@
         <v>1124</v>
       </c>
       <c r="B777" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C777" t="s">
         <v>1125</v>
       </c>
-      <c r="C777" t="s">
+      <c r="D777" t="s">
         <v>371</v>
       </c>
       <c r="G777">
@@ -26161,9 +26195,12 @@
         <v>1124</v>
       </c>
       <c r="B778" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C778" t="s">
         <v>1125</v>
       </c>
-      <c r="C778" t="s">
+      <c r="D778" t="s">
         <v>1770</v>
       </c>
       <c r="G778">
@@ -26181,9 +26218,12 @@
         <v>1124</v>
       </c>
       <c r="B779" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C779" t="s">
         <v>1125</v>
       </c>
-      <c r="C779" t="s">
+      <c r="D779" t="s">
         <v>367</v>
       </c>
       <c r="G779">
@@ -26201,15 +26241,18 @@
         <v>1124</v>
       </c>
       <c r="B780" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C780" t="s">
         <v>1125</v>
       </c>
-      <c r="C780" t="s">
+      <c r="D780" t="s">
         <v>368</v>
       </c>
-      <c r="D780" t="s">
+      <c r="E780" t="s">
         <v>1276</v>
       </c>
-      <c r="E780" t="s">
+      <c r="F780" t="s">
         <v>1127</v>
       </c>
       <c r="G780">
@@ -26227,15 +26270,18 @@
         <v>1124</v>
       </c>
       <c r="B781" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C781" t="s">
         <v>1125</v>
       </c>
-      <c r="C781" t="s">
+      <c r="D781" t="s">
         <v>368</v>
       </c>
-      <c r="D781" t="s">
+      <c r="E781" t="s">
         <v>1276</v>
       </c>
-      <c r="E781" t="s">
+      <c r="F781" t="s">
         <v>1126</v>
       </c>
       <c r="G781">
@@ -26253,15 +26299,18 @@
         <v>1124</v>
       </c>
       <c r="B782" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C782" t="s">
         <v>1125</v>
       </c>
-      <c r="C782" t="s">
+      <c r="D782" t="s">
         <v>368</v>
       </c>
-      <c r="D782" t="s">
+      <c r="E782" t="s">
         <v>1275</v>
       </c>
-      <c r="E782" t="s">
+      <c r="F782" t="s">
         <v>1128</v>
       </c>
       <c r="G782">
@@ -26279,15 +26328,18 @@
         <v>1124</v>
       </c>
       <c r="B783" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C783" t="s">
         <v>1125</v>
       </c>
-      <c r="C783" t="s">
+      <c r="D783" t="s">
         <v>368</v>
       </c>
-      <c r="D783" t="s">
+      <c r="E783" t="s">
         <v>1275</v>
       </c>
-      <c r="E783" t="s">
+      <c r="F783" t="s">
         <v>1274</v>
       </c>
       <c r="G783">
@@ -26305,9 +26357,12 @@
         <v>1124</v>
       </c>
       <c r="B784" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C784" t="s">
         <v>1125</v>
       </c>
-      <c r="C784" t="s">
+      <c r="D784" t="s">
         <v>366</v>
       </c>
       <c r="G784">
@@ -26325,12 +26380,15 @@
         <v>1124</v>
       </c>
       <c r="B785" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C785" t="s">
         <v>1125</v>
       </c>
-      <c r="C785" t="s">
+      <c r="D785" t="s">
         <v>369</v>
       </c>
-      <c r="D785" t="s">
+      <c r="E785" t="s">
         <v>2152</v>
       </c>
       <c r="G785">
@@ -26348,15 +26406,18 @@
         <v>1124</v>
       </c>
       <c r="B786" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C786" t="s">
         <v>1125</v>
       </c>
-      <c r="C786" t="s">
+      <c r="D786" t="s">
         <v>369</v>
       </c>
-      <c r="D786" t="s">
+      <c r="E786" t="s">
         <v>2151</v>
       </c>
-      <c r="E786" t="s">
+      <c r="F786" t="s">
         <v>1130</v>
       </c>
       <c r="G786">
@@ -26374,15 +26435,18 @@
         <v>1124</v>
       </c>
       <c r="B787" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C787" t="s">
         <v>1125</v>
       </c>
-      <c r="C787" t="s">
+      <c r="D787" t="s">
         <v>369</v>
       </c>
-      <c r="D787" t="s">
+      <c r="E787" t="s">
         <v>2151</v>
       </c>
-      <c r="E787" t="s">
+      <c r="F787" t="s">
         <v>1129</v>
       </c>
       <c r="G787">
@@ -26400,9 +26464,12 @@
         <v>1124</v>
       </c>
       <c r="B788" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C788" t="s">
         <v>1125</v>
       </c>
-      <c r="C788" t="s">
+      <c r="D788" t="s">
         <v>364</v>
       </c>
       <c r="G788">
@@ -26420,9 +26487,12 @@
         <v>1124</v>
       </c>
       <c r="B789" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C789" t="s">
         <v>1125</v>
       </c>
-      <c r="C789" t="s">
+      <c r="D789" t="s">
         <v>362</v>
       </c>
       <c r="G789">
@@ -26440,9 +26510,12 @@
         <v>1124</v>
       </c>
       <c r="B790" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C790" t="s">
         <v>1125</v>
       </c>
-      <c r="C790" t="s">
+      <c r="D790" t="s">
         <v>370</v>
       </c>
       <c r="G790">
@@ -26460,9 +26533,12 @@
         <v>1124</v>
       </c>
       <c r="B791" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C791" t="s">
         <v>1125</v>
       </c>
-      <c r="C791" t="s">
+      <c r="D791" t="s">
         <v>1284</v>
       </c>
       <c r="G791">
@@ -26480,9 +26556,12 @@
         <v>1124</v>
       </c>
       <c r="B792" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C792" t="s">
         <v>1125</v>
       </c>
-      <c r="C792" t="s">
+      <c r="D792" t="s">
         <v>363</v>
       </c>
       <c r="G792">
@@ -26500,9 +26579,12 @@
         <v>1124</v>
       </c>
       <c r="B793" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C793" t="s">
         <v>1125</v>
       </c>
-      <c r="C793" t="s">
+      <c r="D793" t="s">
         <v>365</v>
       </c>
       <c r="G793">
@@ -26520,9 +26602,12 @@
         <v>1124</v>
       </c>
       <c r="B794" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C794" t="s">
         <v>1310</v>
       </c>
-      <c r="C794" t="s">
+      <c r="D794" t="s">
         <v>2029</v>
       </c>
       <c r="G794">
@@ -26540,9 +26625,12 @@
         <v>1124</v>
       </c>
       <c r="B795" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C795" t="s">
         <v>1310</v>
       </c>
-      <c r="C795" t="s">
+      <c r="D795" t="s">
         <v>2028</v>
       </c>
       <c r="G795">
@@ -26560,9 +26648,12 @@
         <v>1124</v>
       </c>
       <c r="B796" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C796" t="s">
         <v>1132</v>
       </c>
-      <c r="C796" t="s">
+      <c r="D796" t="s">
         <v>375</v>
       </c>
       <c r="G796">
@@ -26580,9 +26671,12 @@
         <v>1124</v>
       </c>
       <c r="B797" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C797" t="s">
         <v>1132</v>
       </c>
-      <c r="C797" t="s">
+      <c r="D797" t="s">
         <v>376</v>
       </c>
       <c r="G797">
@@ -26600,12 +26694,15 @@
         <v>1124</v>
       </c>
       <c r="B798" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C798" t="s">
         <v>1132</v>
       </c>
-      <c r="C798" t="s">
+      <c r="D798" t="s">
         <v>374</v>
       </c>
-      <c r="D798" t="s">
+      <c r="E798" t="s">
         <v>866</v>
       </c>
       <c r="G798">
@@ -26623,12 +26720,15 @@
         <v>1124</v>
       </c>
       <c r="B799" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C799" t="s">
         <v>1132</v>
       </c>
-      <c r="C799" t="s">
+      <c r="D799" t="s">
         <v>374</v>
       </c>
-      <c r="D799" t="s">
+      <c r="E799" t="s">
         <v>865</v>
       </c>
       <c r="G799">
@@ -26646,12 +26746,15 @@
         <v>1124</v>
       </c>
       <c r="B800" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C800" t="s">
         <v>1132</v>
       </c>
-      <c r="C800" t="s">
+      <c r="D800" t="s">
         <v>374</v>
       </c>
-      <c r="D800" t="s">
+      <c r="E800" t="s">
         <v>864</v>
       </c>
       <c r="G800">
@@ -26669,12 +26772,15 @@
         <v>1124</v>
       </c>
       <c r="B801" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C801" t="s">
         <v>1132</v>
       </c>
-      <c r="C801" t="s">
+      <c r="D801" t="s">
         <v>374</v>
       </c>
-      <c r="D801" t="s">
+      <c r="E801" t="s">
         <v>863</v>
       </c>
       <c r="G801">
@@ -26692,12 +26798,15 @@
         <v>1124</v>
       </c>
       <c r="B802" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C802" t="s">
         <v>1132</v>
       </c>
-      <c r="C802" t="s">
+      <c r="D802" t="s">
         <v>374</v>
       </c>
-      <c r="D802" t="s">
+      <c r="E802" t="s">
         <v>862</v>
       </c>
       <c r="G802">
@@ -26715,9 +26824,12 @@
         <v>1124</v>
       </c>
       <c r="B803" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C803" t="s">
         <v>97</v>
       </c>
-      <c r="C803" t="s">
+      <c r="D803" t="s">
         <v>1857</v>
       </c>
       <c r="G803">
@@ -26735,9 +26847,12 @@
         <v>1124</v>
       </c>
       <c r="B804" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C804" t="s">
         <v>97</v>
       </c>
-      <c r="C804" t="s">
+      <c r="D804" t="s">
         <v>1858</v>
       </c>
       <c r="G804">
@@ -26755,9 +26870,12 @@
         <v>1124</v>
       </c>
       <c r="B805" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C805" t="s">
         <v>98</v>
       </c>
-      <c r="C805" t="s">
+      <c r="D805" t="s">
         <v>389</v>
       </c>
       <c r="G805">
@@ -26775,9 +26893,12 @@
         <v>1124</v>
       </c>
       <c r="B806" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C806" t="s">
         <v>98</v>
       </c>
-      <c r="C806" t="s">
+      <c r="D806" t="s">
         <v>390</v>
       </c>
       <c r="G806">
@@ -26795,9 +26916,12 @@
         <v>1124</v>
       </c>
       <c r="B807" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C807" t="s">
         <v>98</v>
       </c>
-      <c r="C807" t="s">
+      <c r="D807" t="s">
         <v>388</v>
       </c>
       <c r="G807">
@@ -26815,9 +26939,12 @@
         <v>1124</v>
       </c>
       <c r="B808" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C808" t="s">
         <v>98</v>
       </c>
-      <c r="C808" t="s">
+      <c r="D808" t="s">
         <v>394</v>
       </c>
       <c r="G808">
@@ -26835,9 +26962,12 @@
         <v>1124</v>
       </c>
       <c r="B809" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C809" t="s">
         <v>98</v>
       </c>
-      <c r="C809" t="s">
+      <c r="D809" t="s">
         <v>393</v>
       </c>
       <c r="G809">
@@ -26855,9 +26985,12 @@
         <v>1124</v>
       </c>
       <c r="B810" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C810" t="s">
         <v>98</v>
       </c>
-      <c r="C810" t="s">
+      <c r="D810" t="s">
         <v>1134</v>
       </c>
       <c r="G810">
@@ -26875,9 +27008,12 @@
         <v>1124</v>
       </c>
       <c r="B811" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C811" t="s">
         <v>98</v>
       </c>
-      <c r="C811" t="s">
+      <c r="D811" t="s">
         <v>395</v>
       </c>
       <c r="G811">
@@ -26895,9 +27031,12 @@
         <v>1124</v>
       </c>
       <c r="B812" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C812" t="s">
         <v>98</v>
       </c>
-      <c r="C812" t="s">
+      <c r="D812" t="s">
         <v>401</v>
       </c>
       <c r="G812">
@@ -26915,9 +27054,12 @@
         <v>1124</v>
       </c>
       <c r="B813" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C813" t="s">
         <v>98</v>
       </c>
-      <c r="C813" t="s">
+      <c r="D813" t="s">
         <v>392</v>
       </c>
       <c r="G813">
@@ -26935,9 +27077,12 @@
         <v>1124</v>
       </c>
       <c r="B814" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C814" t="s">
         <v>98</v>
       </c>
-      <c r="C814" t="s">
+      <c r="D814" t="s">
         <v>391</v>
       </c>
       <c r="G814">
@@ -26955,9 +27100,12 @@
         <v>1124</v>
       </c>
       <c r="B815" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C815" t="s">
         <v>98</v>
       </c>
-      <c r="C815" t="s">
+      <c r="D815" t="s">
         <v>399</v>
       </c>
       <c r="G815">
@@ -26975,9 +27123,12 @@
         <v>1124</v>
       </c>
       <c r="B816" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C816" t="s">
         <v>98</v>
       </c>
-      <c r="C816" t="s">
+      <c r="D816" t="s">
         <v>397</v>
       </c>
       <c r="G816">
@@ -26995,9 +27146,12 @@
         <v>1124</v>
       </c>
       <c r="B817" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C817" t="s">
         <v>98</v>
       </c>
-      <c r="C817" t="s">
+      <c r="D817" t="s">
         <v>398</v>
       </c>
       <c r="G817">
@@ -27015,9 +27169,12 @@
         <v>1124</v>
       </c>
       <c r="B818" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C818" t="s">
         <v>98</v>
       </c>
-      <c r="C818" t="s">
+      <c r="D818" t="s">
         <v>396</v>
       </c>
       <c r="G818">
@@ -27035,9 +27192,12 @@
         <v>1124</v>
       </c>
       <c r="B819" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C819" t="s">
         <v>98</v>
       </c>
-      <c r="C819" t="s">
+      <c r="D819" t="s">
         <v>400</v>
       </c>
       <c r="G819">
@@ -27055,15 +27215,18 @@
         <v>1124</v>
       </c>
       <c r="B820" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C820" t="s">
         <v>1380</v>
       </c>
-      <c r="C820" t="s">
+      <c r="D820" t="s">
         <v>892</v>
       </c>
-      <c r="D820" t="s">
+      <c r="E820" t="s">
         <v>1043</v>
       </c>
-      <c r="E820" t="s">
+      <c r="F820" t="s">
         <v>1694</v>
       </c>
       <c r="G820">
@@ -27081,15 +27244,18 @@
         <v>1124</v>
       </c>
       <c r="B821" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C821" t="s">
         <v>1380</v>
       </c>
-      <c r="C821" t="s">
+      <c r="D821" t="s">
         <v>892</v>
       </c>
-      <c r="D821" t="s">
+      <c r="E821" t="s">
         <v>1043</v>
       </c>
-      <c r="E821" t="s">
+      <c r="F821" t="s">
         <v>1695</v>
       </c>
       <c r="G821">
@@ -27107,12 +27273,15 @@
         <v>1124</v>
       </c>
       <c r="B822" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C822" t="s">
         <v>1380</v>
       </c>
-      <c r="C822" t="s">
+      <c r="D822" t="s">
         <v>892</v>
       </c>
-      <c r="D822" t="s">
+      <c r="E822" t="s">
         <v>1042</v>
       </c>
       <c r="G822">
@@ -27130,12 +27299,15 @@
         <v>1124</v>
       </c>
       <c r="B823" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C823" t="s">
         <v>1380</v>
       </c>
-      <c r="C823" t="s">
+      <c r="D823" t="s">
         <v>892</v>
       </c>
-      <c r="D823" t="s">
+      <c r="E823" t="s">
         <v>1041</v>
       </c>
       <c r="G823">
@@ -27153,6 +27325,9 @@
         <v>1124</v>
       </c>
       <c r="B824" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C824" t="s">
         <v>372</v>
       </c>
       <c r="G824">
@@ -27170,9 +27345,12 @@
         <v>1124</v>
       </c>
       <c r="B825" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C825" t="s">
         <v>1131</v>
       </c>
-      <c r="C825" t="s">
+      <c r="D825" t="s">
         <v>1460</v>
       </c>
       <c r="G825">
@@ -27190,9 +27368,12 @@
         <v>1124</v>
       </c>
       <c r="B826" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C826" t="s">
         <v>1131</v>
       </c>
-      <c r="C826" t="s">
+      <c r="D826" t="s">
         <v>373</v>
       </c>
       <c r="G826">
@@ -27210,9 +27391,12 @@
         <v>1124</v>
       </c>
       <c r="B827" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C827" t="s">
         <v>1131</v>
       </c>
-      <c r="C827" t="s">
+      <c r="D827" t="s">
         <v>1617</v>
       </c>
       <c r="G827">
@@ -27230,9 +27414,12 @@
         <v>1124</v>
       </c>
       <c r="B828" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C828" t="s">
         <v>1131</v>
       </c>
-      <c r="C828" t="s">
+      <c r="D828" t="s">
         <v>1618</v>
       </c>
       <c r="G828">
@@ -27250,9 +27437,12 @@
         <v>1124</v>
       </c>
       <c r="B829" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C829" t="s">
         <v>1131</v>
       </c>
-      <c r="C829" t="s">
+      <c r="D829" t="s">
         <v>1619</v>
       </c>
       <c r="G829">
@@ -27270,9 +27460,12 @@
         <v>1124</v>
       </c>
       <c r="B830" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C830" t="s">
         <v>1131</v>
       </c>
-      <c r="C830" t="s">
+      <c r="D830" t="s">
         <v>1620</v>
       </c>
       <c r="G830">
@@ -45549,7 +45742,7 @@
   <conditionalFormatting sqref="C1343">
     <cfRule type="duplicateValues" dxfId="21" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1624:C1048576 F408:F409 F195:F210 D1450 E920 F1619 E1620 F1615 E1612 F1611 E1608 F1607 E1604 D1199:D1217 C1534:C1536 C1538:C1539 E322:E324 C1522:C1524 D1112:D1118 E1111 D1060:D1067 E1100:E1106 E1068:E1079 C1258 B1259:B1261 E1218:E1220 D730:D732 D500:D502 D930:D933 D938:D955 D1306 D272 D106 C368:D368 C928:C929 D915:D927 E902 E234:E235 E238 D2:D4 C1 D617 D741 D1324:D1325 E1349 D1327:D1329 D6:D23 C385:C399 B586 C366:C367 C1026 D1049 E1036:E1045 F1034 D1031 E1032:E1033 C1028:C1030 D1025 D1051:D1055 E1284 C958:C964 C967:C978 C1004:C1017 D1018:D1022 D979:D989 B1272:B1273 D1511 C1334:C1342 C936:D937 D1121:D1125 D1138:D1190 D1195:D1197 E1191:E1194 E1126:E1137 E1377:E1385 E1529 C1367:C1370 C1344:C1345 E1606 E1610 E1618 E1622 C275:C286 C1301:D1302 C1320:C1322 C1319:D1319 D1356:D1358 E1087 D1476:D1484 D1486:D1491 D884:D899 B287:B299 C431:C438 E402:E424 C401 F419:F420 F417 D839:D840 C1526:D1526 E1527 C1527:C1532 C1537:D1537 C1542:C1564 D1283:D1289 D1291:D1292 D1359:E1360 D864:D867 D630:D642 D589 D1349:D1353 C990:C996 D36:D41 D266:D269 D1485:E1485 D763:D765 B698 D701:D702 C587:C618 D619 D597:D599 C1492:C1510 D232:D237 D195:D226 D743 C1512:C1516 D1313:D1315 C1303:C1305 C349:C364 D438:D444 F446 C1451:D1452 E1437:E1438 E326 C1272 C300:C302 D399:D430 C456:C499 D373:D374 C369:C383 D304:D326 C304 C303:D303 C334:C342 D329:D332 D1569:D1571 E1414 D691:D692 D1080:D1110 C1276:C1298 C1307:C1318 E1238:E1240 D1221:D1257 D901:D906 D506 C501:C510 D513 D1371:D1400 D1411:D1414 E1021 D647:D649 C699:C702 C704:C710 B703 D851:D853 D858:D859 D855 D711:D718 D1527:D1531 C620:C646 C511:D511 E241:E242 D239:D246 C1346:E1346 E1616 E1614 D1587:D1623 D995:D1002 C1566:C1585 D1453:E1453 C1417:C1433 C1435:C1450 D1442:E1442 D1436:D1446 E1443 E1457:E1460 C1453:C1474 D652:D656 D831 C1347:C1365 C650:C697 D670 C227:C272 D722 D545:D550 C512:C585 E546:E549 D1404:D1408 C719:C768 B769:C770 B851 C771:C825 C827:C850 B826 C906:C914 D907:E907 C5:C194 C852:C883 C1032:C1035 D1046 D668">
+  <conditionalFormatting sqref="C769:D770 C1624:C1048576 F408:F409 F195:F210 D1450 E920 F1619 E1620 F1615 E1612 F1611 E1608 F1607 E1604 D1199:D1217 C1534:C1536 C1538:C1539 E322:E324 C1522:C1524 D1112:D1118 E1111 D1060:D1067 E1100:E1106 E1068:E1079 C1258 B1259:B1261 E1218:E1220 D730:D732 D500:D502 D930:D933 D938:D955 D1306 D272 D106 C368:D368 C928:C929 D915:D927 E902 E234:E235 E238 D2:D4 C1 D617 D741 D1324:D1325 E1349 D1327:D1329 D6:D23 C385:C399 B586 C366:C367 C1026 D1049 E1036:E1045 F1034 D1031 E1032:E1033 C1028:C1030 D1025 D1051:D1055 E1284 C958:C964 C967:C978 C1004:C1017 D1018:D1022 D979:D989 B1272:B1273 D1511 C1334:C1342 C936:D937 D1121:D1125 D1138:D1190 D1195:D1197 E1191:E1194 E1126:E1137 E1377:E1385 E1529 C1367:C1370 C1344:C1345 E1606 E1610 E1618 E1622 C275:C286 C1301:D1302 C1320:C1322 C1319:D1319 D1356:D1358 E1087 D1476:D1484 D1486:D1491 D884:D899 B287:B299 C431:C438 E402:E424 C401 F419:F420 F417 D839:D840 C1526:D1526 E1527 C1527:C1532 C1537:D1537 C1542:C1564 D1283:D1289 D1291:D1292 D1359:E1360 D864:D867 D630:D642 D589 D1349:D1353 C990:C996 D36:D41 D266:D269 D1485:E1485 D763:D765 B698 D701:D702 C587:C618 D619 D597:D599 C1492:C1510 D232:D237 D195:D226 D743 C1512:C1516 D1313:D1315 C1303:C1305 C349:C364 D438:D444 F446 C1451:D1452 E1437:E1438 E326 C1272 C300:C302 D399:D430 C456:C499 D373:D374 C369:C383 D304:D326 C304 C303:D303 C334:C342 D329:D332 D1569:D1571 E1414 D691:D692 D1080:D1110 C1276:C1298 C1307:C1318 E1238:E1240 D1221:D1257 D901:D906 D506 C501:C510 D513 D1371:D1400 D1411:D1414 E1021 D647:D649 C699:C702 C704:C710 B703 D851:D853 D858:D859 D855 D711:D718 D1527:D1531 C620:C646 C511:D511 E241:E242 D239:D246 C1346:E1346 E1616 E1614 D1587:D1623 D995:D1002 C1566:C1585 D1453:E1453 C1417:C1433 C1435:C1450 D1442:E1442 D1436:D1446 E1443 E1457:E1460 C1453:C1474 D652:D656 C1347:C1365 C650:C697 D670 C227:C272 D722 D545:D550 C512:C585 E546:E549 D1404:D1408 C719:C767 D768 B851 D771:D825 C831:C850 D827:D831 C826 C906:C914 D907:E907 C5:C194 C852:C883 C1032:C1035 D1046 D668">
     <cfRule type="duplicateValues" dxfId="20" priority="145"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1270:D1271">

--- a/config/knowledgegraph.xlsx
+++ b/config/knowledgegraph.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\python\NLP\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57170985-1870-42F4-A479-802CAE5C7B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF8A4B76-C141-43B4-8F99-F39A5FBB252E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7373,10 +7373,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>右后降支|后降支|右后降</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>桡骨茎突</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -7494,6 +7490,10 @@
   </si>
   <si>
     <t>上腹</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>右后降支|后降支|右后降|左室后支</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -9129,7 +9129,7 @@
         <v>2113</v>
       </c>
       <c r="C42" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="D42" t="s">
         <v>749</v>
@@ -9152,7 +9152,7 @@
         <v>2113</v>
       </c>
       <c r="C43" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="D43" t="s">
         <v>751</v>
@@ -9175,7 +9175,7 @@
         <v>2113</v>
       </c>
       <c r="C44" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="D44" t="s">
         <v>750</v>
@@ -9201,7 +9201,7 @@
         <v>2113</v>
       </c>
       <c r="C45" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="D45" t="s">
         <v>750</v>
@@ -9227,7 +9227,7 @@
         <v>2113</v>
       </c>
       <c r="C46" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="D46" t="s">
         <v>738</v>
@@ -9250,7 +9250,7 @@
         <v>2113</v>
       </c>
       <c r="C47" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="D47" t="s">
         <v>739</v>
@@ -9273,7 +9273,7 @@
         <v>2113</v>
       </c>
       <c r="C48" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="D48" t="s">
         <v>1018</v>
@@ -9296,7 +9296,7 @@
         <v>2113</v>
       </c>
       <c r="C49" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="D49" t="s">
         <v>1019</v>
@@ -11857,7 +11857,7 @@
         <v>204</v>
       </c>
       <c r="D149" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="E149" t="s">
         <v>963</v>
@@ -11883,7 +11883,7 @@
         <v>204</v>
       </c>
       <c r="D150" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="E150" t="s">
         <v>964</v>
@@ -11909,7 +11909,7 @@
         <v>204</v>
       </c>
       <c r="D151" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="E151" t="s">
         <v>962</v>
@@ -11935,7 +11935,7 @@
         <v>204</v>
       </c>
       <c r="D152" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="E152" t="s">
         <v>1438</v>
@@ -16872,7 +16872,7 @@
         <v>1568</v>
       </c>
       <c r="B360" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C360" t="s">
         <v>231</v>
@@ -16892,7 +16892,7 @@
         <v>1568</v>
       </c>
       <c r="B361" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C361" t="s">
         <v>233</v>
@@ -16912,7 +16912,7 @@
         <v>1568</v>
       </c>
       <c r="B362" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C362" t="s">
         <v>234</v>
@@ -16932,7 +16932,7 @@
         <v>1568</v>
       </c>
       <c r="B363" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C363" t="s">
         <v>232</v>
@@ -16952,7 +16952,7 @@
         <v>1568</v>
       </c>
       <c r="B364" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C364" t="s">
         <v>228</v>
@@ -16972,7 +16972,7 @@
         <v>1568</v>
       </c>
       <c r="B365" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C365" t="s">
         <v>1585</v>
@@ -16995,7 +16995,7 @@
         <v>1568</v>
       </c>
       <c r="B366" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C366" t="s">
         <v>229</v>
@@ -17018,7 +17018,7 @@
         <v>1568</v>
       </c>
       <c r="B367" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C367" t="s">
         <v>229</v>
@@ -17041,7 +17041,7 @@
         <v>1568</v>
       </c>
       <c r="B368" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C368" t="s">
         <v>229</v>
@@ -17064,7 +17064,7 @@
         <v>1568</v>
       </c>
       <c r="B369" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C369" t="s">
         <v>229</v>
@@ -17087,7 +17087,7 @@
         <v>1568</v>
       </c>
       <c r="B370" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C370" t="s">
         <v>229</v>
@@ -17110,7 +17110,7 @@
         <v>1568</v>
       </c>
       <c r="B371" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C371" t="s">
         <v>229</v>
@@ -17133,7 +17133,7 @@
         <v>1568</v>
       </c>
       <c r="B372" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C372" t="s">
         <v>229</v>
@@ -17156,7 +17156,7 @@
         <v>1568</v>
       </c>
       <c r="B373" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C373" t="s">
         <v>229</v>
@@ -17179,7 +17179,7 @@
         <v>1568</v>
       </c>
       <c r="B374" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C374" t="s">
         <v>229</v>
@@ -22028,7 +22028,7 @@
         <v>1337</v>
       </c>
       <c r="D589" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="E589" t="s">
         <v>1236</v>
@@ -23735,7 +23735,7 @@
         <v>1455</v>
       </c>
       <c r="D667" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="E667" t="s">
         <v>1732</v>
@@ -25965,10 +25965,10 @@
         <v>1124</v>
       </c>
       <c r="B768" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C768" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="D768" t="s">
         <v>899</v>
@@ -25988,10 +25988,10 @@
         <v>1124</v>
       </c>
       <c r="B769" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C769" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="D769" t="s">
         <v>894</v>
@@ -26011,10 +26011,10 @@
         <v>1124</v>
       </c>
       <c r="B770" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C770" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="D770" t="s">
         <v>1819</v>
@@ -26034,10 +26034,10 @@
         <v>1124</v>
       </c>
       <c r="B771" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C771" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="D771" t="s">
         <v>1818</v>
@@ -26057,10 +26057,10 @@
         <v>1124</v>
       </c>
       <c r="B772" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C772" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="D772" t="s">
         <v>1817</v>
@@ -26080,10 +26080,10 @@
         <v>1124</v>
       </c>
       <c r="B773" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C773" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="D773" t="s">
         <v>897</v>
@@ -26103,10 +26103,10 @@
         <v>1124</v>
       </c>
       <c r="B774" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C774" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="D774" t="s">
         <v>896</v>
@@ -26126,10 +26126,10 @@
         <v>1124</v>
       </c>
       <c r="B775" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C775" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="D775" t="s">
         <v>898</v>
@@ -26149,13 +26149,13 @@
         <v>1124</v>
       </c>
       <c r="B776" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C776" t="s">
         <v>1125</v>
       </c>
       <c r="D776" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="G776">
         <v>106</v>
@@ -26172,7 +26172,7 @@
         <v>1124</v>
       </c>
       <c r="B777" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C777" t="s">
         <v>1125</v>
@@ -26195,7 +26195,7 @@
         <v>1124</v>
       </c>
       <c r="B778" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C778" t="s">
         <v>1125</v>
@@ -26218,7 +26218,7 @@
         <v>1124</v>
       </c>
       <c r="B779" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C779" t="s">
         <v>1125</v>
@@ -26241,7 +26241,7 @@
         <v>1124</v>
       </c>
       <c r="B780" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C780" t="s">
         <v>1125</v>
@@ -26270,7 +26270,7 @@
         <v>1124</v>
       </c>
       <c r="B781" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C781" t="s">
         <v>1125</v>
@@ -26299,7 +26299,7 @@
         <v>1124</v>
       </c>
       <c r="B782" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C782" t="s">
         <v>1125</v>
@@ -26328,7 +26328,7 @@
         <v>1124</v>
       </c>
       <c r="B783" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C783" t="s">
         <v>1125</v>
@@ -26357,7 +26357,7 @@
         <v>1124</v>
       </c>
       <c r="B784" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C784" t="s">
         <v>1125</v>
@@ -26380,7 +26380,7 @@
         <v>1124</v>
       </c>
       <c r="B785" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C785" t="s">
         <v>1125</v>
@@ -26389,7 +26389,7 @@
         <v>369</v>
       </c>
       <c r="E785" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="G785">
         <v>106</v>
@@ -26406,7 +26406,7 @@
         <v>1124</v>
       </c>
       <c r="B786" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C786" t="s">
         <v>1125</v>
@@ -26415,7 +26415,7 @@
         <v>369</v>
       </c>
       <c r="E786" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="F786" t="s">
         <v>1130</v>
@@ -26435,7 +26435,7 @@
         <v>1124</v>
       </c>
       <c r="B787" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C787" t="s">
         <v>1125</v>
@@ -26444,7 +26444,7 @@
         <v>369</v>
       </c>
       <c r="E787" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="F787" t="s">
         <v>1129</v>
@@ -26464,7 +26464,7 @@
         <v>1124</v>
       </c>
       <c r="B788" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C788" t="s">
         <v>1125</v>
@@ -26487,7 +26487,7 @@
         <v>1124</v>
       </c>
       <c r="B789" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C789" t="s">
         <v>1125</v>
@@ -26510,7 +26510,7 @@
         <v>1124</v>
       </c>
       <c r="B790" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C790" t="s">
         <v>1125</v>
@@ -26533,7 +26533,7 @@
         <v>1124</v>
       </c>
       <c r="B791" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C791" t="s">
         <v>1125</v>
@@ -26556,7 +26556,7 @@
         <v>1124</v>
       </c>
       <c r="B792" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C792" t="s">
         <v>1125</v>
@@ -26579,7 +26579,7 @@
         <v>1124</v>
       </c>
       <c r="B793" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C793" t="s">
         <v>1125</v>
@@ -26602,7 +26602,7 @@
         <v>1124</v>
       </c>
       <c r="B794" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C794" t="s">
         <v>1310</v>
@@ -26625,7 +26625,7 @@
         <v>1124</v>
       </c>
       <c r="B795" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C795" t="s">
         <v>1310</v>
@@ -26648,7 +26648,7 @@
         <v>1124</v>
       </c>
       <c r="B796" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C796" t="s">
         <v>1132</v>
@@ -26671,7 +26671,7 @@
         <v>1124</v>
       </c>
       <c r="B797" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C797" t="s">
         <v>1132</v>
@@ -26694,7 +26694,7 @@
         <v>1124</v>
       </c>
       <c r="B798" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C798" t="s">
         <v>1132</v>
@@ -26720,7 +26720,7 @@
         <v>1124</v>
       </c>
       <c r="B799" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C799" t="s">
         <v>1132</v>
@@ -26746,7 +26746,7 @@
         <v>1124</v>
       </c>
       <c r="B800" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C800" t="s">
         <v>1132</v>
@@ -26772,7 +26772,7 @@
         <v>1124</v>
       </c>
       <c r="B801" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C801" t="s">
         <v>1132</v>
@@ -26798,7 +26798,7 @@
         <v>1124</v>
       </c>
       <c r="B802" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C802" t="s">
         <v>1132</v>
@@ -26824,7 +26824,7 @@
         <v>1124</v>
       </c>
       <c r="B803" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C803" t="s">
         <v>97</v>
@@ -26847,7 +26847,7 @@
         <v>1124</v>
       </c>
       <c r="B804" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C804" t="s">
         <v>97</v>
@@ -26870,7 +26870,7 @@
         <v>1124</v>
       </c>
       <c r="B805" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C805" t="s">
         <v>98</v>
@@ -26893,7 +26893,7 @@
         <v>1124</v>
       </c>
       <c r="B806" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C806" t="s">
         <v>98</v>
@@ -26916,7 +26916,7 @@
         <v>1124</v>
       </c>
       <c r="B807" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C807" t="s">
         <v>98</v>
@@ -26939,7 +26939,7 @@
         <v>1124</v>
       </c>
       <c r="B808" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C808" t="s">
         <v>98</v>
@@ -26962,7 +26962,7 @@
         <v>1124</v>
       </c>
       <c r="B809" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C809" t="s">
         <v>98</v>
@@ -26985,7 +26985,7 @@
         <v>1124</v>
       </c>
       <c r="B810" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C810" t="s">
         <v>98</v>
@@ -27008,7 +27008,7 @@
         <v>1124</v>
       </c>
       <c r="B811" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C811" t="s">
         <v>98</v>
@@ -27031,7 +27031,7 @@
         <v>1124</v>
       </c>
       <c r="B812" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C812" t="s">
         <v>98</v>
@@ -27054,7 +27054,7 @@
         <v>1124</v>
       </c>
       <c r="B813" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C813" t="s">
         <v>98</v>
@@ -27077,7 +27077,7 @@
         <v>1124</v>
       </c>
       <c r="B814" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C814" t="s">
         <v>98</v>
@@ -27100,7 +27100,7 @@
         <v>1124</v>
       </c>
       <c r="B815" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C815" t="s">
         <v>98</v>
@@ -27123,7 +27123,7 @@
         <v>1124</v>
       </c>
       <c r="B816" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C816" t="s">
         <v>98</v>
@@ -27146,7 +27146,7 @@
         <v>1124</v>
       </c>
       <c r="B817" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C817" t="s">
         <v>98</v>
@@ -27169,7 +27169,7 @@
         <v>1124</v>
       </c>
       <c r="B818" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C818" t="s">
         <v>98</v>
@@ -27192,7 +27192,7 @@
         <v>1124</v>
       </c>
       <c r="B819" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C819" t="s">
         <v>98</v>
@@ -27215,7 +27215,7 @@
         <v>1124</v>
       </c>
       <c r="B820" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C820" t="s">
         <v>1380</v>
@@ -27244,7 +27244,7 @@
         <v>1124</v>
       </c>
       <c r="B821" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C821" t="s">
         <v>1380</v>
@@ -27273,7 +27273,7 @@
         <v>1124</v>
       </c>
       <c r="B822" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C822" t="s">
         <v>1380</v>
@@ -27299,7 +27299,7 @@
         <v>1124</v>
       </c>
       <c r="B823" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C823" t="s">
         <v>1380</v>
@@ -27325,7 +27325,7 @@
         <v>1124</v>
       </c>
       <c r="B824" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C824" t="s">
         <v>372</v>
@@ -27345,7 +27345,7 @@
         <v>1124</v>
       </c>
       <c r="B825" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C825" t="s">
         <v>1131</v>
@@ -27368,7 +27368,7 @@
         <v>1124</v>
       </c>
       <c r="B826" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C826" t="s">
         <v>1131</v>
@@ -27391,7 +27391,7 @@
         <v>1124</v>
       </c>
       <c r="B827" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C827" t="s">
         <v>1131</v>
@@ -27414,7 +27414,7 @@
         <v>1124</v>
       </c>
       <c r="B828" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C828" t="s">
         <v>1131</v>
@@ -27437,7 +27437,7 @@
         <v>1124</v>
       </c>
       <c r="B829" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C829" t="s">
         <v>1131</v>
@@ -27460,7 +27460,7 @@
         <v>1124</v>
       </c>
       <c r="B830" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C830" t="s">
         <v>1131</v>
@@ -27776,7 +27776,7 @@
         <v>381</v>
       </c>
       <c r="F844" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="G844" s="2">
         <v>106.5</v>
@@ -27805,7 +27805,7 @@
         <v>381</v>
       </c>
       <c r="F845" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="G845" s="2">
         <v>106.5</v>
@@ -27834,7 +27834,7 @@
         <v>381</v>
       </c>
       <c r="F846" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="G846" s="2">
         <v>106.5</v>
@@ -28049,7 +28049,7 @@
         <v>1133</v>
       </c>
       <c r="C856" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="D856" t="s">
         <v>378</v>
@@ -28072,7 +28072,7 @@
         <v>1133</v>
       </c>
       <c r="C857" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="D857" t="s">
         <v>379</v>
@@ -28135,7 +28135,7 @@
         <v>1430</v>
       </c>
       <c r="C860" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="G860" s="2">
         <v>106.5</v>
@@ -28155,7 +28155,7 @@
         <v>1430</v>
       </c>
       <c r="C861" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="G861" s="2">
         <v>106.5</v>
@@ -29112,7 +29112,7 @@
         <v>2015</v>
       </c>
       <c r="E906" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="G906">
         <v>108</v>
@@ -29138,7 +29138,7 @@
         <v>2015</v>
       </c>
       <c r="E907" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="G907">
         <v>108</v>
@@ -29164,7 +29164,7 @@
         <v>2015</v>
       </c>
       <c r="E908" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="G908">
         <v>108</v>
@@ -31657,7 +31657,7 @@
         <v>1784</v>
       </c>
       <c r="C1016" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="D1016" t="s">
         <v>1381</v>
@@ -31683,7 +31683,7 @@
         <v>1784</v>
       </c>
       <c r="C1017" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="D1017" t="s">
         <v>1381</v>
@@ -31712,7 +31712,7 @@
         <v>1784</v>
       </c>
       <c r="C1018" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="D1018" t="s">
         <v>1381</v>
@@ -31741,10 +31741,10 @@
         <v>1784</v>
       </c>
       <c r="C1019" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="D1019" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="E1019" t="s">
         <v>130</v>
@@ -32362,13 +32362,13 @@
         <v>1785</v>
       </c>
       <c r="B1046" t="s">
+        <v>2163</v>
+      </c>
+      <c r="C1046" t="s">
         <v>2164</v>
       </c>
-      <c r="C1046" t="s">
-        <v>2165</v>
-      </c>
       <c r="D1046" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="E1046" t="s">
         <v>888</v>
@@ -32388,13 +32388,13 @@
         <v>1785</v>
       </c>
       <c r="B1047" t="s">
+        <v>2163</v>
+      </c>
+      <c r="C1047" t="s">
         <v>2164</v>
       </c>
-      <c r="C1047" t="s">
-        <v>2165</v>
-      </c>
       <c r="D1047" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="E1047" t="s">
         <v>889</v>
@@ -40464,7 +40464,7 @@
         <v>1802</v>
       </c>
       <c r="D1398" t="s">
-        <v>2135</v>
+        <v>2166</v>
       </c>
       <c r="G1398">
         <v>405</v>
@@ -40473,7 +40473,7 @@
         <v>406</v>
       </c>
       <c r="I1398">
-        <v>18</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1399" spans="1:9" x14ac:dyDescent="0.15">
@@ -42795,7 +42795,7 @@
         <v>1489</v>
       </c>
       <c r="C1497" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="G1497">
         <v>504.5</v>
@@ -73972,7 +73972,7 @@
     </row>
     <row r="1289" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1289" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1289" t="s">
         <v>1154</v>
@@ -73992,7 +73992,7 @@
     </row>
     <row r="1290" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1290" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1290" t="s">
         <v>1154</v>
@@ -74015,7 +74015,7 @@
     </row>
     <row r="1291" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1291" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1291" t="s">
         <v>1154</v>
@@ -74038,7 +74038,7 @@
     </row>
     <row r="1292" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1292" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1292" t="s">
         <v>1154</v>
@@ -74061,7 +74061,7 @@
     </row>
     <row r="1293" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1293" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1293" t="s">
         <v>1154</v>
@@ -74084,7 +74084,7 @@
     </row>
     <row r="1294" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1294" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1294" t="s">
         <v>1154</v>
@@ -74107,7 +74107,7 @@
     </row>
     <row r="1295" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1295" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1295" t="s">
         <v>1154</v>
@@ -74130,7 +74130,7 @@
     </row>
     <row r="1296" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1296" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1296" t="s">
         <v>1154</v>
@@ -74153,7 +74153,7 @@
     </row>
     <row r="1297" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1297" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1297" t="s">
         <v>1154</v>
@@ -74176,7 +74176,7 @@
     </row>
     <row r="1298" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1298" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1298" t="s">
         <v>1154</v>
@@ -74202,7 +74202,7 @@
     </row>
     <row r="1299" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1299" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1299" t="s">
         <v>1154</v>
@@ -74228,7 +74228,7 @@
     </row>
     <row r="1300" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1300" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1300" t="s">
         <v>1154</v>
@@ -74254,7 +74254,7 @@
     </row>
     <row r="1301" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1301" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1301" t="s">
         <v>1154</v>
@@ -74280,7 +74280,7 @@
     </row>
     <row r="1302" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1302" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1302" t="s">
         <v>1154</v>
@@ -74306,7 +74306,7 @@
     </row>
     <row r="1303" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1303" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1303" t="s">
         <v>1154</v>
@@ -74332,7 +74332,7 @@
     </row>
     <row r="1304" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1304" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1304" t="s">
         <v>1154</v>
@@ -74358,7 +74358,7 @@
     </row>
     <row r="1305" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1305" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1305" t="s">
         <v>1154</v>
@@ -74384,7 +74384,7 @@
     </row>
     <row r="1306" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1306" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1306" t="s">
         <v>1154</v>
@@ -74410,7 +74410,7 @@
     </row>
     <row r="1307" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1307" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1307" t="s">
         <v>1154</v>
@@ -74433,7 +74433,7 @@
     </row>
     <row r="1308" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1308" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1308" t="s">
         <v>1154</v>
@@ -74456,7 +74456,7 @@
     </row>
     <row r="1309" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1309" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1309" t="s">
         <v>95</v>
@@ -74476,7 +74476,7 @@
     </row>
     <row r="1310" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1310" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1310" t="s">
         <v>95</v>
@@ -74496,7 +74496,7 @@
     </row>
     <row r="1311" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1311" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1311" t="s">
         <v>95</v>
@@ -74516,7 +74516,7 @@
     </row>
     <row r="1312" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1312" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1312" t="s">
         <v>96</v>
@@ -74536,7 +74536,7 @@
     </row>
     <row r="1313" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1313" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1313" t="s">
         <v>96</v>
@@ -74556,7 +74556,7 @@
     </row>
     <row r="1314" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1314" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1314" t="s">
         <v>96</v>
@@ -74576,7 +74576,7 @@
     </row>
     <row r="1315" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1315" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1315" t="s">
         <v>96</v>
@@ -74596,7 +74596,7 @@
     </row>
     <row r="1316" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1316" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1316" t="s">
         <v>88</v>
@@ -74616,7 +74616,7 @@
     </row>
     <row r="1317" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1317" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1317" t="s">
         <v>88</v>
@@ -74636,7 +74636,7 @@
     </row>
     <row r="1318" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1318" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1318" t="s">
         <v>88</v>
@@ -74656,7 +74656,7 @@
     </row>
     <row r="1319" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1319" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1319" t="s">
         <v>1089</v>
@@ -74676,7 +74676,7 @@
     </row>
     <row r="1320" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1320" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1320" t="s">
         <v>1089</v>
@@ -74696,7 +74696,7 @@
     </row>
     <row r="1321" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1321" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1321" t="s">
         <v>1089</v>
@@ -74716,7 +74716,7 @@
     </row>
     <row r="1322" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1322" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1322" t="s">
         <v>1089</v>
@@ -74736,7 +74736,7 @@
     </row>
     <row r="1323" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1323" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1323" t="s">
         <v>1089</v>
@@ -74756,7 +74756,7 @@
     </row>
     <row r="1324" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1324" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1324" t="s">
         <v>1089</v>
@@ -74776,7 +74776,7 @@
     </row>
     <row r="1325" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1325" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1325" t="s">
         <v>1089</v>
@@ -74796,7 +74796,7 @@
     </row>
     <row r="1326" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1326" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1326" t="s">
         <v>1088</v>
@@ -74819,7 +74819,7 @@
     </row>
     <row r="1327" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1327" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1327" t="s">
         <v>1088</v>
@@ -74839,7 +74839,7 @@
     </row>
     <row r="1328" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1328" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1328" t="s">
         <v>1088</v>
@@ -74862,7 +74862,7 @@
     </row>
     <row r="1329" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1329" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1329" t="s">
         <v>1088</v>
@@ -74885,7 +74885,7 @@
     </row>
     <row r="1330" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1330" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1330" t="s">
         <v>1569</v>
@@ -74911,7 +74911,7 @@
     </row>
     <row r="1331" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1331" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1331" t="s">
         <v>1569</v>
@@ -74937,7 +74937,7 @@
     </row>
     <row r="1332" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1332" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1332" t="s">
         <v>1569</v>
@@ -74963,7 +74963,7 @@
     </row>
     <row r="1333" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1333" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1333" t="s">
         <v>1569</v>
@@ -74992,7 +74992,7 @@
     </row>
     <row r="1334" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1334" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1334" t="s">
         <v>1569</v>
@@ -75021,7 +75021,7 @@
     </row>
     <row r="1335" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1335" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1335" t="s">
         <v>1569</v>
@@ -75050,7 +75050,7 @@
     </row>
     <row r="1336" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1336" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1336" t="s">
         <v>1569</v>
@@ -75079,7 +75079,7 @@
     </row>
     <row r="1337" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1337" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1337" t="s">
         <v>1569</v>
@@ -75108,7 +75108,7 @@
     </row>
     <row r="1338" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1338" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1338" t="s">
         <v>1569</v>
@@ -75137,7 +75137,7 @@
     </row>
     <row r="1339" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1339" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1339" t="s">
         <v>1569</v>
@@ -75160,7 +75160,7 @@
     </row>
     <row r="1340" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1340" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1340" t="s">
         <v>1569</v>
@@ -75183,7 +75183,7 @@
     </row>
     <row r="1341" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1341" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1341" t="s">
         <v>1569</v>
@@ -75209,7 +75209,7 @@
     </row>
     <row r="1342" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1342" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1342" t="s">
         <v>1569</v>
@@ -75235,7 +75235,7 @@
     </row>
     <row r="1343" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1343" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1343" t="s">
         <v>1569</v>
@@ -75261,7 +75261,7 @@
     </row>
     <row r="1344" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1344" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1344" t="s">
         <v>1569</v>
@@ -75287,7 +75287,7 @@
     </row>
     <row r="1345" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1345" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1345" t="s">
         <v>1569</v>
@@ -75313,7 +75313,7 @@
     </row>
     <row r="1346" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1346" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1346" t="s">
         <v>1569</v>
@@ -75336,7 +75336,7 @@
     </row>
     <row r="1347" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1347" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1347" t="s">
         <v>1569</v>
@@ -75359,7 +75359,7 @@
     </row>
     <row r="1348" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1348" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1348" t="s">
         <v>1569</v>
@@ -75385,7 +75385,7 @@
     </row>
     <row r="1349" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1349" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1349" t="s">
         <v>1569</v>
@@ -75411,7 +75411,7 @@
     </row>
     <row r="1350" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1350" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1350" t="s">
         <v>1569</v>
@@ -75434,7 +75434,7 @@
     </row>
     <row r="1351" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1351" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1351" t="s">
         <v>1569</v>
@@ -76959,7 +76959,7 @@
         <v>1355</v>
       </c>
       <c r="E1422" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="G1422">
         <v>506.5</v>
@@ -78614,7 +78614,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -78628,7 +78628,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -78642,7 +78642,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -78656,7 +78656,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -78670,7 +78670,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="B31">
         <v>1</v>

--- a/config/knowledgegraph.xlsx
+++ b/config/knowledgegraph.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\python\NLP\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF8A4B76-C141-43B4-8F99-F39A5FBB252E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DDD140-8CBB-4D5B-8C31-3B1451B65E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12054" uniqueCount="2167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12060" uniqueCount="2167">
   <si>
     <t>一级部位</t>
   </si>
@@ -39209,9 +39209,12 @@
         <v>1186</v>
       </c>
       <c r="C1342" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1342" t="s">
         <v>1365</v>
       </c>
-      <c r="D1342" t="s">
+      <c r="E1342" t="s">
         <v>937</v>
       </c>
       <c r="G1342">
@@ -39232,9 +39235,12 @@
         <v>1186</v>
       </c>
       <c r="C1343" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1343" t="s">
         <v>1365</v>
       </c>
-      <c r="D1343" t="s">
+      <c r="E1343" t="s">
         <v>936</v>
       </c>
       <c r="G1343">
@@ -39255,9 +39261,12 @@
         <v>1186</v>
       </c>
       <c r="C1344" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1344" t="s">
         <v>1365</v>
       </c>
-      <c r="D1344" t="s">
+      <c r="E1344" t="s">
         <v>938</v>
       </c>
       <c r="G1344">
@@ -39278,9 +39287,12 @@
         <v>1186</v>
       </c>
       <c r="C1345" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1345" t="s">
         <v>1365</v>
       </c>
-      <c r="D1345" t="s">
+      <c r="E1345" t="s">
         <v>1367</v>
       </c>
       <c r="G1345">
@@ -39301,12 +39313,15 @@
         <v>1186</v>
       </c>
       <c r="C1346" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1346" t="s">
         <v>1365</v>
       </c>
-      <c r="D1346" t="s">
+      <c r="E1346" t="s">
         <v>1366</v>
       </c>
-      <c r="E1346" t="s">
+      <c r="F1346" t="s">
         <v>2061</v>
       </c>
       <c r="G1346">
@@ -39373,6 +39388,9 @@
         <v>1186</v>
       </c>
       <c r="C1349" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1349" t="s">
         <v>572</v>
       </c>
       <c r="G1349">
@@ -45739,10 +45757,10 @@
     <sortCondition ref="E2:E1623"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="C1343">
+  <conditionalFormatting sqref="D1343">
     <cfRule type="duplicateValues" dxfId="21" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C769:D770 C1624:C1048576 F408:F409 F195:F210 D1450 E920 F1619 E1620 F1615 E1612 F1611 E1608 F1607 E1604 D1199:D1217 C1534:C1536 C1538:C1539 E322:E324 C1522:C1524 D1112:D1118 E1111 D1060:D1067 E1100:E1106 E1068:E1079 C1258 B1259:B1261 E1218:E1220 D730:D732 D500:D502 D930:D933 D938:D955 D1306 D272 D106 C368:D368 C928:C929 D915:D927 E902 E234:E235 E238 D2:D4 C1 D617 D741 D1324:D1325 E1349 D1327:D1329 D6:D23 C385:C399 B586 C366:C367 C1026 D1049 E1036:E1045 F1034 D1031 E1032:E1033 C1028:C1030 D1025 D1051:D1055 E1284 C958:C964 C967:C978 C1004:C1017 D1018:D1022 D979:D989 B1272:B1273 D1511 C1334:C1342 C936:D937 D1121:D1125 D1138:D1190 D1195:D1197 E1191:E1194 E1126:E1137 E1377:E1385 E1529 C1367:C1370 C1344:C1345 E1606 E1610 E1618 E1622 C275:C286 C1301:D1302 C1320:C1322 C1319:D1319 D1356:D1358 E1087 D1476:D1484 D1486:D1491 D884:D899 B287:B299 C431:C438 E402:E424 C401 F419:F420 F417 D839:D840 C1526:D1526 E1527 C1527:C1532 C1537:D1537 C1542:C1564 D1283:D1289 D1291:D1292 D1359:E1360 D864:D867 D630:D642 D589 D1349:D1353 C990:C996 D36:D41 D266:D269 D1485:E1485 D763:D765 B698 D701:D702 C587:C618 D619 D597:D599 C1492:C1510 D232:D237 D195:D226 D743 C1512:C1516 D1313:D1315 C1303:C1305 C349:C364 D438:D444 F446 C1451:D1452 E1437:E1438 E326 C1272 C300:C302 D399:D430 C456:C499 D373:D374 C369:C383 D304:D326 C304 C303:D303 C334:C342 D329:D332 D1569:D1571 E1414 D691:D692 D1080:D1110 C1276:C1298 C1307:C1318 E1238:E1240 D1221:D1257 D901:D906 D506 C501:C510 D513 D1371:D1400 D1411:D1414 E1021 D647:D649 C699:C702 C704:C710 B703 D851:D853 D858:D859 D855 D711:D718 D1527:D1531 C620:C646 C511:D511 E241:E242 D239:D246 C1346:E1346 E1616 E1614 D1587:D1623 D995:D1002 C1566:C1585 D1453:E1453 C1417:C1433 C1435:C1450 D1442:E1442 D1436:D1446 E1443 E1457:E1460 C1453:C1474 D652:D656 C1347:C1365 C650:C697 D670 C227:C272 D722 D545:D550 C512:C585 E546:E549 D1404:D1408 C719:C767 D768 B851 D771:D825 C831:C850 D827:D831 C826 C906:C914 D907:E907 C5:C194 C852:C883 C1032:C1035 D1046 D668">
+  <conditionalFormatting sqref="D1344:D1345 C769:D770 C1624:C1048576 F408:F409 F195:F210 D1450 E920 F1619 E1620 F1615 E1612 F1611 E1608 F1607 E1604 D1199:D1217 C1534:C1536 C1538:C1539 E322:E324 C1522:C1524 D1112:D1118 E1111 D1060:D1067 E1100:E1106 E1068:E1079 C1258 B1259:B1261 E1218:E1220 D730:D732 D500:D502 D930:D933 D938:D955 D1306 D272 D106 C368:D368 C928:C929 D915:D927 E902 E234:E235 E238 D2:D4 C1 D617 D741 D1324:D1325 E1349 D1327:D1329 D6:D23 C385:C399 B586 C366:C367 C1026 D1049 E1036:E1045 F1034 D1031 E1032:E1033 C1028:C1030 D1025 D1051:D1055 E1284 C958:C964 C967:C978 C1004:C1017 D1018:D1022 D979:D989 B1272:B1273 D1511 C1334:C1341 C936:D937 D1121:D1125 D1138:D1190 D1195:D1197 E1191:E1194 E1126:E1137 E1377:E1385 E1529 C1367:C1370 E1606 E1610 E1618 E1622 C275:C286 C1301:D1302 C1320:C1322 C1319:D1319 D1356:D1358 E1087 D1476:D1484 D1486:D1491 D884:D899 B287:B299 C431:C438 E402:E424 C401 F419:F420 F417 D839:D840 C1526:D1526 E1527 C1527:C1532 C1537:D1537 C1542:C1564 D1283:D1289 D1291:D1292 D1359:E1360 D864:D867 D630:D642 D589 C990:C996 D36:D41 D266:D269 D1485:E1485 D763:D765 B698 D701:D702 C587:C618 D619 D597:D599 C1492:C1510 D232:D237 D195:D226 D743 C1512:C1516 D1313:D1315 C1303:C1305 C349:C364 D438:D444 F446 C1451:D1452 E1437:E1438 E326 C1272 C300:C302 D399:D430 C456:C499 D373:D374 C369:C383 D304:D326 C304 C303:D303 C334:C342 D329:D332 D1569:D1571 E1414 D691:D692 D1080:D1110 C1276:C1298 C1307:C1318 E1238:E1240 D1221:D1257 D901:D906 D506 C501:C510 D513 D1371:D1400 D1411:D1414 E1021 D647:D649 C699:C702 C704:C710 B703 D851:D853 D858:D859 D855 D711:D718 D1527:D1531 C620:C646 C511:D511 E241:E242 D239:D246 D1346:F1346 E1616 E1614 D1587:D1623 D995:D1002 C1566:C1585 D1453:E1453 C1417:C1433 C1435:C1450 D1442:E1442 D1436:D1446 E1443 E1457:E1460 C1453:C1474 D652:D656 D1349:D1353 C650:C697 D670 C227:C272 D722 D545:D550 C512:C585 E546:E549 D1404:D1408 C719:C767 D768 B851 D771:D825 C831:C850 D827:D831 C826 C906:C914 D907:E907 C5:C194 C852:C883 C1032:C1035 D1046 D668 C1342:D1342 C1343:C1365">
     <cfRule type="duplicateValues" dxfId="20" priority="145"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1270:D1271">
